--- a/scripts/WOs List.xlsx
+++ b/scripts/WOs List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/884f899eba661abe/Python/Nucleus/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A73EA27CCB385EDFDA183B74D128BCA7531CB0C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD973736-0739-4580-BA7C-D4870B3B1B05}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_A73EA27CCB385EDFDA183B74D128BCA7531CB0C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D3ACABD-2A9B-45ED-8BB2-9D99400D620E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26530" uniqueCount="7235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26913" uniqueCount="7235">
   <si>
     <t>Número de WO</t>
   </si>
@@ -23534,7 +23534,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -23864,7 +23875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI758"/>
+  <dimension ref="A1:AI1149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -105008,8 +105019,1926 @@
         <v>38</v>
       </c>
     </row>
+    <row r="767" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="K767" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="768" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="K768" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="769" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K769" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="770" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K770" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="771" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K771" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="772" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K772" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="773" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K773" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="774" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K774" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="775" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K775" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="776" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K776" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="777" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K777" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="778" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K778" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="779" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K779" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="780" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K780" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="781" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K781" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="782" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K782" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="783" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K783" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="784" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K784" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="785" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K785" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="786" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K786" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="787" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K787" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="788" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K788" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="789" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K789" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="790" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K790" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="791" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K791" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="792" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K792" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="793" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K793" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="794" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K794" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="795" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K795" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="796" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K796" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="797" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K797" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="798" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K798" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="799" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K799" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="800" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K800" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="801" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K801" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="802" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K802" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="803" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K803" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="804" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K804" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="805" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K805" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="806" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K806" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="807" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K807" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="808" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K808" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="809" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K809" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="810" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K810" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="811" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K811" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="812" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K812" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="813" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K813" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="814" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K814" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="815" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K815" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="816" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K816" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="817" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K817" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="818" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K818" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="819" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K819" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="820" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K820" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="821" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K821" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="822" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K822" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="823" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K823" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="824" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K824" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="825" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K825" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="826" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K826" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="827" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K827" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="828" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K828" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="829" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K829" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="830" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K830" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="831" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K831" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="832" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K832" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="833" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K833" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="834" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K834" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="835" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K835" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="836" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K836" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="837" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K837" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="838" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K838" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="839" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K839" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="840" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K840" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="841" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K841" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="842" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K842" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="843" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K843" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="844" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K844" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="845" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K845" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="846" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K846" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="847" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K847" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="848" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K848" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="849" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K849" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="850" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K850" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="851" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K851" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="852" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K852" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="853" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K853" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="854" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K854" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="855" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K855" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="856" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K856" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="857" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K857" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="858" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K858" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="859" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K859" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="860" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K860" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="861" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K861" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="862" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K862" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="863" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K863" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="864" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K864" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="865" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K865" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="866" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K866" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="867" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K867" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="868" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K868" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="869" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K869" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="870" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K870" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="871" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K871" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="872" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K872" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="873" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K873" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="874" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K874" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="875" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K875" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="876" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K876" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="877" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K877" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="878" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K878" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="879" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K879" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="880" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K880" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="881" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K881" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="882" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K882" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="883" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K883" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="884" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K884" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="885" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K885" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="886" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K886" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="887" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K887" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="888" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K888" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="889" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K889" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="890" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K890" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="891" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K891" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="892" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K892" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="893" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K893" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="894" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K894" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="895" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K895" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="896" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K896" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="897" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K897" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="898" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K898" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="899" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K899" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="900" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K900" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="901" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K901" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="902" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K902" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="903" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K903" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="904" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K904" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="905" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K905" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="906" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K906" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="907" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K907" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="908" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K908" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="909" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K909" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="910" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K910" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="911" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K911" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="912" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K912" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="913" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K913" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="914" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K914" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="915" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K915" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="916" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K916" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="917" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K917" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="918" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K918" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="919" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K919" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="920" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K920" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="921" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K921" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="922" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K922" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="923" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K923" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="924" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K924" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="925" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K925" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="926" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K926" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="927" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K927" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="928" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K928" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="929" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K929" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="930" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K930" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="931" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K931" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="932" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K932" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="933" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K933" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="934" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K934" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="935" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K935" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="936" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K936" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="937" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K937" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="938" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K938" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="939" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K939" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="940" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K940" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="941" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K941" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="942" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K942" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="943" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K943" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="944" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K944" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="945" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K945" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="946" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K946" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="947" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K947" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="948" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K948" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="949" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K949" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="950" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K950" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="951" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K951" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="952" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K952" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="953" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K953" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="954" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K954" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="955" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K955" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="956" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K956" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="957" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K957" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="958" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K958" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="959" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K959" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="960" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K960" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="961" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K961" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="962" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K962" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="963" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K963" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="964" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K964" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="965" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K965" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="966" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K966" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="967" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K967" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="968" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K968" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="969" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K969" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="970" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K970" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="971" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K971" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="972" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K972" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="973" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K973" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="974" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K974" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="975" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K975" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="976" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K976" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="977" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K977" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="978" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K978" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="979" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K979" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="980" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K980" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="981" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K981" t="s">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="982" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K982" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="983" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K983" t="s">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="984" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K984" t="s">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="985" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K985" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="986" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K986" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="987" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K987" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="988" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K988" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="989" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K989" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="990" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K990" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="991" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K991" t="s">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="992" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K992" t="s">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="993" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K993" t="s">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="994" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K994" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="995" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K995" t="s">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="996" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K996" t="s">
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="997" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K997" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="998" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K998" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="999" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K999" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="1000" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1000" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="1001" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1001" t="s">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="1002" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1002" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="1003" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1003" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="1004" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1004" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="1005" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1005" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="1006" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1006" t="s">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="1007" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1007" t="s">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="1008" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1008" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="1009" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1009" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="1010" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1010" t="s">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="1011" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1011" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="1012" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1012" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="1013" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1013" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="1014" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1014" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="1015" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1015" t="s">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="1016" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1016" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="1017" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1017" t="s">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="1018" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1018" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="1019" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1019" t="s">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="1020" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1020" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="1021" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1021" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="1022" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1022" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="1023" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1023" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="1024" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1024" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="1025" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1025" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="1026" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1026" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="1027" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1027" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="1028" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1028" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="1029" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1029" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="1030" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1030" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="1031" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1031" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="1032" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1032" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1033" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1033" t="s">
+        <v>4239</v>
+      </c>
+    </row>
+    <row r="1034" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1034" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="1035" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1035" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="1036" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1036" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="1037" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1037" t="s">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="1038" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1038" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="1039" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1039" t="s">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="1040" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1040" t="s">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="1041" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1041" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="1042" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1042" t="s">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="1043" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1043" t="s">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="1044" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1044" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="1045" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1045" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="1046" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1046" t="s">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="1047" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1047" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="1048" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1048" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="1049" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1049" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="1050" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1050" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="1051" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1051" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="1052" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1052" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1053" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1053" t="s">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="1054" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1054" t="s">
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="1055" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1055" t="s">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="1056" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1056" t="s">
+        <v>4707</v>
+      </c>
+    </row>
+    <row r="1057" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1057" t="s">
+        <v>4721</v>
+      </c>
+    </row>
+    <row r="1058" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1058" t="s">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="1059" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1059" t="s">
+        <v>4789</v>
+      </c>
+    </row>
+    <row r="1060" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1060" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="1061" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1061" t="s">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="1062" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1062" t="s">
+        <v>4870</v>
+      </c>
+    </row>
+    <row r="1063" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1063" t="s">
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="1064" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1064" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="1065" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1065" t="s">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="1066" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1066" t="s">
+        <v>4969</v>
+      </c>
+    </row>
+    <row r="1067" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1067" t="s">
+        <v>4995</v>
+      </c>
+    </row>
+    <row r="1068" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1068" t="s">
+        <v>5029</v>
+      </c>
+    </row>
+    <row r="1069" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1069" t="s">
+        <v>5042</v>
+      </c>
+    </row>
+    <row r="1070" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1070" t="s">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="1071" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1071" t="s">
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="1072" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1072" t="s">
+        <v>5153</v>
+      </c>
+    </row>
+    <row r="1073" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1073" t="s">
+        <v>5161</v>
+      </c>
+    </row>
+    <row r="1074" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1074" t="s">
+        <v>5188</v>
+      </c>
+    </row>
+    <row r="1075" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1075" t="s">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="1076" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1076" t="s">
+        <v>5244</v>
+      </c>
+    </row>
+    <row r="1077" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1077" t="s">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="1078" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1078" t="s">
+        <v>5301</v>
+      </c>
+    </row>
+    <row r="1079" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1079" t="s">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="1080" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1080" t="s">
+        <v>5352</v>
+      </c>
+    </row>
+    <row r="1081" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1081" t="s">
+        <v>5440</v>
+      </c>
+    </row>
+    <row r="1082" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1082" t="s">
+        <v>5476</v>
+      </c>
+    </row>
+    <row r="1083" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1083" t="s">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="1084" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1084" t="s">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="1085" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1085" t="s">
+        <v>5542</v>
+      </c>
+    </row>
+    <row r="1086" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1086" t="s">
+        <v>5552</v>
+      </c>
+    </row>
+    <row r="1087" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1087" t="s">
+        <v>5581</v>
+      </c>
+    </row>
+    <row r="1088" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1088" t="s">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="1089" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1089" t="s">
+        <v>5604</v>
+      </c>
+    </row>
+    <row r="1090" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1090" t="s">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="1091" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1091" t="s">
+        <v>5646</v>
+      </c>
+    </row>
+    <row r="1092" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1092" t="s">
+        <v>5659</v>
+      </c>
+    </row>
+    <row r="1093" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1093" t="s">
+        <v>5674</v>
+      </c>
+    </row>
+    <row r="1094" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1094" t="s">
+        <v>5685</v>
+      </c>
+    </row>
+    <row r="1095" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1095" t="s">
+        <v>5710</v>
+      </c>
+    </row>
+    <row r="1096" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1096" t="s">
+        <v>5720</v>
+      </c>
+    </row>
+    <row r="1097" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1097" t="s">
+        <v>5741</v>
+      </c>
+    </row>
+    <row r="1098" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1098" t="s">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="1099" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1099" t="s">
+        <v>5758</v>
+      </c>
+    </row>
+    <row r="1100" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1100" t="s">
+        <v>5767</v>
+      </c>
+    </row>
+    <row r="1101" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1101" t="s">
+        <v>5777</v>
+      </c>
+    </row>
+    <row r="1102" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1102" t="s">
+        <v>5790</v>
+      </c>
+    </row>
+    <row r="1103" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1103" t="s">
+        <v>5802</v>
+      </c>
+    </row>
+    <row r="1104" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1104" t="s">
+        <v>5840</v>
+      </c>
+    </row>
+    <row r="1105" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1105" t="s">
+        <v>5888</v>
+      </c>
+    </row>
+    <row r="1106" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1106" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="1107" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1107" t="s">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="1108" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1108" t="s">
+        <v>5939</v>
+      </c>
+    </row>
+    <row r="1109" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1109" t="s">
+        <v>5975</v>
+      </c>
+    </row>
+    <row r="1110" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1110" t="s">
+        <v>6020</v>
+      </c>
+    </row>
+    <row r="1111" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1111" t="s">
+        <v>6039</v>
+      </c>
+    </row>
+    <row r="1112" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1112" t="s">
+        <v>6079</v>
+      </c>
+    </row>
+    <row r="1113" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1113" t="s">
+        <v>6104</v>
+      </c>
+    </row>
+    <row r="1114" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1114" t="s">
+        <v>6152</v>
+      </c>
+    </row>
+    <row r="1115" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1115" t="s">
+        <v>6191</v>
+      </c>
+    </row>
+    <row r="1116" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1116" t="s">
+        <v>6247</v>
+      </c>
+    </row>
+    <row r="1117" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1117" t="s">
+        <v>6267</v>
+      </c>
+    </row>
+    <row r="1118" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1118" t="s">
+        <v>6276</v>
+      </c>
+    </row>
+    <row r="1119" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1119" t="s">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="1120" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1120" t="s">
+        <v>6310</v>
+      </c>
+    </row>
+    <row r="1121" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1121" t="s">
+        <v>6352</v>
+      </c>
+    </row>
+    <row r="1122" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1122" t="s">
+        <v>6379</v>
+      </c>
+    </row>
+    <row r="1123" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1123" t="s">
+        <v>6418</v>
+      </c>
+    </row>
+    <row r="1124" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1124" t="s">
+        <v>6431</v>
+      </c>
+    </row>
+    <row r="1125" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1125" t="s">
+        <v>6441</v>
+      </c>
+    </row>
+    <row r="1126" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1126" t="s">
+        <v>6458</v>
+      </c>
+    </row>
+    <row r="1127" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1127" t="s">
+        <v>6487</v>
+      </c>
+    </row>
+    <row r="1128" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1128" t="s">
+        <v>6516</v>
+      </c>
+    </row>
+    <row r="1129" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1129" t="s">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="1130" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1130" t="s">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="1131" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1131" t="s">
+        <v>6637</v>
+      </c>
+    </row>
+    <row r="1132" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1132" t="s">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="1133" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1133" t="s">
+        <v>6679</v>
+      </c>
+    </row>
+    <row r="1134" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1134" t="s">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="1135" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1135" t="s">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="1136" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1136" t="s">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="1137" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1137" t="s">
+        <v>6783</v>
+      </c>
+    </row>
+    <row r="1138" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1138" t="s">
+        <v>6792</v>
+      </c>
+    </row>
+    <row r="1139" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1139" t="s">
+        <v>6802</v>
+      </c>
+    </row>
+    <row r="1140" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1140" t="s">
+        <v>6827</v>
+      </c>
+    </row>
+    <row r="1141" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1141" t="s">
+        <v>6846</v>
+      </c>
+    </row>
+    <row r="1142" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1142" t="s">
+        <v>6865</v>
+      </c>
+    </row>
+    <row r="1143" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1143" t="s">
+        <v>6907</v>
+      </c>
+    </row>
+    <row r="1144" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1144" t="s">
+        <v>7058</v>
+      </c>
+    </row>
+    <row r="1145" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1145" t="s">
+        <v>7102</v>
+      </c>
+    </row>
+    <row r="1146" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1146" t="s">
+        <v>7131</v>
+      </c>
+    </row>
+    <row r="1147" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1147" t="s">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="1148" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1148" t="s">
+        <v>7161</v>
+      </c>
+    </row>
+    <row r="1149" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K1149" t="s">
+        <v>7182</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AI758" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>